--- a/data/sars/alaska/tables/Alaska_2003_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2003_Appendix2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Desktop/sar_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1574D81F-BE1B-304D-9ECE-8B46DE52E2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5820F8E-AE42-AC4C-8B57-04CAF8434221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3080" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{28F0FA3F-B6AC-1F4B-94BA-ED9675D2952C}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="71">
   <si>
     <t>Alaska</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>comments</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -381,7 +387,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -559,6 +565,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -722,7 +734,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -737,6 +749,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1114,17 +1141,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F18A3D-9C8A-914C-B89E-9132F39E451B}">
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" style="1" customWidth="1"/>
     <col min="2" max="2" width="25.33203125" style="1" customWidth="1"/>
-    <col min="3" max="14" width="10.83203125" style="1"/>
-    <col min="15" max="15" width="10.83203125" style="4"/>
-    <col min="16" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="15" width="10.83203125" style="1"/>
+    <col min="16" max="16" width="10.83203125" style="4"/>
+    <col min="17" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
@@ -1167,11 +1194,14 @@
       <c r="N1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>37</v>
       </c>
@@ -1202,11 +1232,11 @@
       <c r="N2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1238,7 +1268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -1282,7 +1312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1326,7 +1356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1369,11 +1399,11 @@
       <c r="N6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="P6" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1416,87 +1446,95 @@
       <c r="N7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="P7" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="6">
         <v>386</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="6">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="6">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="6">
         <v>359</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="6">
         <v>0.02</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="6">
         <v>0.3</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="6">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1" t="s">
+      <c r="L8" s="6">
+        <v>0</v>
+      </c>
+      <c r="M8" s="6">
+        <v>0</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="O8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" s="7"/>
+    </row>
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="8">
         <v>9860</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="6">
         <v>0.124</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="6">
         <v>0.124</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="8">
         <v>8886</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="6">
         <v>0.02</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="6">
         <v>0.5</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="6">
         <v>89</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="6">
         <v>0.2</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="6">
         <v>58</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P9" s="7"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
@@ -1528,77 +1566,85 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="8">
         <v>83400</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="6">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="6">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="8">
         <v>76874</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="6">
         <v>0.02</v>
       </c>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="2">
+      <c r="J11" s="6">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8">
         <v>1537</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11" s="6">
         <v>37.5</v>
       </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1" t="s">
+      <c r="M11" s="6">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="O11" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" s="7"/>
+    </row>
+    <row r="12" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1">
+      <c r="C12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6">
         <v>0.02</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="6">
         <v>0.1</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="K12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6">
         <v>0.8</v>
       </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1" t="s">
+      <c r="M12" s="6">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P12" s="7"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -1636,148 +1682,157 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="8">
         <v>10947</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="6">
         <v>0.24199999999999999</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="6">
         <v>1.56</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="9">
         <v>0.108</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="6">
         <v>0.27400000000000002</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="8">
         <v>8954</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="6">
         <v>0.02</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="6">
         <v>0.5</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K14" s="6">
         <v>90</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14" s="6">
         <v>3</v>
       </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1" t="s">
+      <c r="M14" s="6">
+        <v>0</v>
+      </c>
+      <c r="N14" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="5" t="s">
+      <c r="O14" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P14" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="8">
         <v>30506</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="6">
         <v>0.214</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="6">
         <v>1.37</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="6">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="6">
         <v>0.30399999999999999</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="8">
         <v>25536</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="6">
         <v>0.02</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="6">
         <v>0.5</v>
       </c>
-      <c r="K15" s="1">
+      <c r="K15" s="6">
         <v>255</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15" s="6">
         <v>25</v>
       </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1" t="s">
+      <c r="M15" s="6">
+        <v>0</v>
+      </c>
+      <c r="N15" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="5" t="s">
+      <c r="O15" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="8">
         <v>47356</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="6">
         <v>0.223</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="6">
         <v>1.337</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="6">
         <v>6.2E-2</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="6">
         <v>0.3</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="8">
         <v>39328</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="6">
         <v>0.02</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="6">
         <v>0.5</v>
       </c>
-      <c r="K16" s="1">
+      <c r="K16" s="6">
         <v>393</v>
       </c>
-      <c r="L16" s="1">
+      <c r="L16" s="6">
         <v>2</v>
       </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1" t="s">
+      <c r="M16" s="6">
+        <v>0</v>
+      </c>
+      <c r="N16" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="O16" s="5" t="s">
+      <c r="O16" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P16" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
@@ -1820,9 +1875,9 @@
       <c r="N17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="5"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="5"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1866,7 +1921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1909,87 +1964,95 @@
       <c r="N19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O19" s="5" t="s">
+      <c r="P19" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="6">
         <v>394</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="6">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="6">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="6">
         <v>367</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="6">
         <v>0.02</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="6">
         <v>0.1</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="6">
         <v>0.7</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20" s="6">
         <v>0.8</v>
       </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1" t="s">
+      <c r="M20" s="6">
+        <v>0</v>
+      </c>
+      <c r="N20" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="O20" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P20" s="7"/>
+    </row>
+    <row r="21" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="8">
         <v>4005</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="6">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="6">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="8">
         <v>3698</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="6">
         <v>0.02</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="6">
         <v>0.1</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="6">
         <v>7.4</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21" s="6">
         <v>4.2</v>
       </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1" t="s">
+      <c r="M21" s="6">
+        <v>0</v>
+      </c>
+      <c r="N21" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P21" s="7"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>33</v>
       </c>
@@ -2024,7 +2087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>20</v>
       </c>
@@ -2061,11 +2124,11 @@
       <c r="N23" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="4" t="s">
+      <c r="P23" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>20</v>
       </c>
@@ -2100,7 +2163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
@@ -2132,80 +2195,88 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="1">
+      <c r="C26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="6">
         <v>0.02</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="6">
         <v>0.1</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="N26" s="1" t="s">
+      <c r="K26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L26" s="6">
+        <v>0</v>
+      </c>
+      <c r="M26" s="6">
+        <v>0</v>
+      </c>
+      <c r="N26" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
+      <c r="O26" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P26" s="7"/>
+    </row>
+    <row r="27" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="8">
         <v>888120</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="6">
         <v>4.4749999999999996</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1">
+      <c r="F27" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="6">
         <v>0.2</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="8">
         <v>751714</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="6">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="6">
         <v>0.5</v>
       </c>
-      <c r="K27" s="2">
+      <c r="K27" s="8">
         <v>16162</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L27" s="6">
         <v>16</v>
       </c>
-      <c r="M27" s="2">
+      <c r="M27" s="8">
         <v>1132</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="N27" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P27" s="7"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2237,7 +2308,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2269,7 +2340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2301,39 +2372,43 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I31" s="1">
+      <c r="C31" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6">
         <v>0.02</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="6">
         <v>0.1</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L31" s="1">
+      <c r="K31" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L31" s="6">
         <v>0.4</v>
       </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1" t="s">
+      <c r="M31" s="6">
+        <v>0</v>
+      </c>
+      <c r="N31" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P31" s="7"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>26</v>
       </c>
@@ -2365,7 +2440,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -2397,69 +2472,77 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="8">
         <v>31028</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="8">
         <v>31028</v>
       </c>
-      <c r="I34" s="1">
+      <c r="I34" s="6">
         <v>0.06</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="6">
         <v>0.75</v>
       </c>
-      <c r="K34" s="2">
+      <c r="K34" s="8">
         <v>1396</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L34" s="6">
         <v>3.7</v>
       </c>
-      <c r="M34" s="1">
+      <c r="M34" s="6">
         <v>2</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="N34" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
+      <c r="O34" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P34" s="7"/>
+    </row>
+    <row r="35" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="8">
         <v>34775</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="8">
         <v>34775</v>
       </c>
-      <c r="I35" s="1">
+      <c r="I35" s="6">
         <v>0.06</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="6">
         <v>0.1</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K35" s="6">
         <v>209</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L35" s="6">
         <v>25.9</v>
       </c>
-      <c r="M35" s="1">
+      <c r="M35" s="6">
         <v>176</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="N35" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="O35" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P35" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
